--- a/sp500_sustainability_data_sources.xlsx
+++ b/sp500_sustainability_data_sources.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabellamueller-vogt/Library/Mobile Documents/com~apple~CloudDocs/08 - side quests/ethack/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alinapopov/Library/Mobile Documents/com~apple~CloudDocs/ethack/ethack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7801BACD-2976-5B42-A074-998DF2755A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8050CF10-BFDD-8045-A827-00F2A576A801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17400" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -1680,7 +1680,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1693,53 +1693,48 @@
       <sz val="14"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1812,6 +1807,12 @@
         <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1840,7 +1841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1903,6 +1904,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2423,6 +2427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:T30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2732,7 +2737,7 @@
       <c r="K5" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="26" t="s">
         <v>109</v>
       </c>
       <c r="M5" s="7" t="s">
@@ -2966,7 +2971,7 @@
         <v>153</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>68</v>
@@ -3012,7 +3017,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="70" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" ht="70" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>160</v>
       </c>
@@ -3075,7 +3080,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>173</v>
       </c>
@@ -3138,7 +3143,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="70" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" ht="70" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>185</v>
       </c>
@@ -3201,7 +3206,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>197</v>
       </c>
@@ -3264,7 +3269,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>209</v>
       </c>
@@ -3327,7 +3332,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>220</v>
       </c>
@@ -3390,7 +3395,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="84" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" ht="84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>233</v>
       </c>
@@ -3453,7 +3458,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>246</v>
       </c>
@@ -3516,7 +3521,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="42" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>254</v>
       </c>
@@ -3579,7 +3584,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
         <v>263</v>
       </c>
@@ -3642,7 +3647,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="70" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" ht="70" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>271</v>
       </c>
@@ -3705,7 +3710,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
         <v>280</v>
       </c>
@@ -3768,7 +3773,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
         <v>289</v>
       </c>
@@ -3831,7 +3836,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="70" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" ht="70" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
         <v>297</v>
       </c>
@@ -3894,7 +3899,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
         <v>305</v>
       </c>
@@ -3957,7 +3962,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="70" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" ht="70" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="s">
         <v>314</v>
       </c>
@@ -4020,7 +4025,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="s">
         <v>322</v>
       </c>
@@ -4083,7 +4088,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>330</v>
       </c>
@@ -4146,7 +4151,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
         <v>341</v>
       </c>
@@ -4209,7 +4214,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
         <v>351</v>
       </c>
@@ -4272,7 +4277,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="56" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7" t="s">
         <v>359</v>
       </c>
@@ -4336,7 +4341,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T30" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:T30" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="1 - Universal"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <legacyDrawing r:id="rId1"/>
@@ -4345,6 +4356,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4446,7 +4458,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="19" t="s">
         <v>376</v>
       </c>
@@ -4736,7 +4748,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="56" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
         <v>424</v>
       </c>
@@ -4765,7 +4777,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="70" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="70" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="22" t="s">
         <v>449</v>
       </c>
@@ -4794,7 +4806,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="56" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
         <v>449</v>
       </c>
@@ -4824,7 +4836,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I16" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:I16" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="P1 Environmental &amp; Resource Efficiency"/>
+        <filter val="P2 Transition &amp; Structural Risk"/>
+        <filter val="P3 Governance &amp; Capital Stewardship"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <filter val="498"/>
+        <filter val="500"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -5084,15 +5110,15 @@
       </c>
       <c r="B24" s="8">
         <f>COUNTIF('Data Sources'!$F$2:$F$30,$A24)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24" s="8">
         <f>IFERROR(ROUND(SUMIF('Data Sources'!$F$2:$F$30,$A24,'Data Sources'!$I$2:$I$30)/COUNTIF('Data Sources'!$F$2:$F$30,$A24),0),0)</f>
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>0.97599999999999998</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -5118,7 +5144,7 @@
       </c>
       <c r="B26" s="8">
         <f>COUNTIF('Data Sources'!$F$2:$F$30,$A26)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" s="8">
         <f>IFERROR(ROUND(SUMIF('Data Sources'!$F$2:$F$30,$A26,'Data Sources'!$I$2:$I$30)/COUNTIF('Data Sources'!$F$2:$F$30,$A26),0),0)</f>
